--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_persistent_filters.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_persistent_filters.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>74.55</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>25.45</v>
       </c>
     </row>
   </sheetData>
